--- a/samples/ss_bdgsel_nubrg_ingest.xlsx
+++ b/samples/ss_bdgsel_nubrg_ingest.xlsx
@@ -767,7 +767,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">

--- a/samples/ss_bdgsel_nubrg_ingest.xlsx
+++ b/samples/ss_bdgsel_nubrg_ingest.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U59"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,7 +744,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Bandung Selatan 500/150 kV</t>
+          <t>IBT 1 Bandung Selatan 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -781,14 +781,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -823,31 +819,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bandung Selatan (bus 150 kV)</t>
+          <t>IBT 2 Bandung Selatan 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 2 BDSLN7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>BDSLN7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>BDSLN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -859,10 +869,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -880,17 +894,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PLTA Rajamandala</t>
+          <t>Bandung Selatan (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KIT_RJMDL</t>
+          <t>BDSLN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -937,17 +951,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rajamandala</t>
+          <t>PLTA Rajamandala</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RJMDL</t>
+          <t>KIT_RJMDL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -973,14 +987,10 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -998,17 +1008,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PLTP Wayang Windu</t>
+          <t>Rajamandala</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KIT_WYWDU</t>
+          <t>RJMDL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1034,10 +1044,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1055,17 +1069,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wayang Windu</t>
+          <t>PLTP Wayang Windu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WYWDU</t>
+          <t>KIT_WYWDU</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1091,14 +1105,10 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1116,12 +1126,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sukaluyu</t>
+          <t>Wayang Windu</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SKLYU</t>
+          <t>WYWDU</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1130,7 +1140,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1142,11 +1152,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>bus section + kopel</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
@@ -1156,10 +1162,14 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1177,12 +1187,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cigereleng</t>
+          <t>Sukaluyu</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CGRLG</t>
+          <t>SKLYU</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1203,7 +1213,11 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
@@ -1234,12 +1248,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dayeuh Kolot</t>
+          <t>Cigereleng</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DYKLT</t>
+          <t>CGRLG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1291,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Panasia</t>
+          <t>Dayeuh Kolot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PNSIA</t>
+          <t>DYKLT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1348,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kiaracondong</t>
+          <t>Panasia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KRCDG</t>
+          <t>PNSIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1384,14 +1398,10 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1409,12 +1419,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cianjur</t>
+          <t>Kiaracondong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CNJUR</t>
+          <t>KRCDG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1423,7 +1433,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1450,7 +1460,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1470,12 +1480,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cibereum</t>
+          <t>Cianjur</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CBERM</t>
+          <t>CNJUR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1506,10 +1516,14 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1527,12 +1541,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Cibereum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BRAGA</t>
+          <t>CBERM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1584,17 +1598,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Cigereleng</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IBT 1 CGRLG</t>
+          <t>BRAGA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1602,33 +1616,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>CGRLG</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CGRLG4</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
@@ -1659,17 +1655,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cigereleng (bus 70 kV)</t>
+          <t>IBT 150/70 kV Cigereleng</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CGRLG4</t>
+          <t>IBT 1 CGRLG</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1677,15 +1673,33 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CGRLG</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CGRLG4</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
@@ -1716,12 +1730,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cikalong</t>
+          <t>Cigereleng (bus 70 kV)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CKLNG</t>
+          <t>CGRLG4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1773,12 +1787,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lamajan</t>
+          <t>Cikalong</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LMJAN</t>
+          <t>CKLNG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1830,12 +1844,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sentosa</t>
+          <t>Lamajan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SNTSA</t>
+          <t>LMJAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1866,14 +1880,10 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1891,12 +1901,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Majalaya</t>
+          <t>Sentosa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MJLYA</t>
+          <t>SNTSA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1905,7 +1915,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1927,10 +1937,14 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1948,12 +1962,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Plengan</t>
+          <t>Majalaya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PLNGN</t>
+          <t>MJLYA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2005,17 +2019,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PLTA Plengan</t>
+          <t>Plengan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KIT_PLNGN</t>
+          <t>PLNGN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2062,17 +2076,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sumedang Raya</t>
+          <t>PLTA Plengan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SMDRA</t>
+          <t>KIT_PLNGN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2119,12 +2133,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pameungpeuk</t>
+          <t>Sumedang Raya</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PMPEK</t>
+          <t>SMDRA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2133,7 +2147,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2176,25 +2190,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GITET New Ujungberung</t>
+          <t>Pameungpeuk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NUBRG7</t>
+          <t>PMPEK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>500 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2223,7 +2237,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>NUBRG</t>
+          <t>BDGSEL</t>
         </is>
       </c>
     </row>
@@ -2233,51 +2247,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IBT 1,2 New Ujungberung 500/150 kV</t>
+          <t>GITET New Ujungberung</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IBT 1 NUBRG7</t>
+          <t>NUBRG7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GITET</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>500/150 kV</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>NUBRG7</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>NUBRG5</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
@@ -2287,14 +2283,10 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2312,31 +2304,45 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New Ujungberung (bus 150 kV)</t>
+          <t>IBT 1 New Ujungberung 500/150 kV</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>IBT 1 NUBRG7</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NUBRG7</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>NUBRG5</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -2348,10 +2354,14 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2369,31 +2379,45 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nanjung Rancaekek Baru</t>
+          <t>IBT 2 New Ujungberung 500/150 kV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NRKBA</t>
+          <t>IBT 2 NUBRG7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NUBRG7</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NUBRG5</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2405,10 +2429,14 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2426,17 +2454,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PLTP Kamojang</t>
+          <t>New Ujungberung (bus 150 kV)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KIT_KMJNG</t>
+          <t>NUBRG5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2483,12 +2511,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kamojang</t>
+          <t>Nanjung Rancaekek Baru</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KMJNG</t>
+          <t>NRKBA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2519,14 +2547,10 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2544,12 +2568,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PLTP Darajat</t>
+          <t>PLTP Kamojang</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KIT_DRJAT</t>
+          <t>KIT_KMJNG</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2601,12 +2625,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Darajat</t>
+          <t>Kamojang</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DRJAT</t>
+          <t>KMJNG</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2637,10 +2661,14 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2658,12 +2686,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PLTA Jatigede</t>
+          <t>PLTP Darajat</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KIT_JTDGE</t>
+          <t>KIT_DRJAT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2715,12 +2743,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jatigede</t>
+          <t>Darajat</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JTDGE</t>
+          <t>DRJAT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2751,14 +2779,10 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2776,21 +2800,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cikasungka</t>
+          <t>PLTA Jatigede</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CKSKA</t>
+          <t>KIT_JTDGE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2833,12 +2857,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rancaekek</t>
+          <t>Jatigede</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RCKEK</t>
+          <t>JTDGE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2847,7 +2871,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2869,10 +2893,14 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2890,12 +2918,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rancaekek Baru</t>
+          <t>Cikasungka</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RCKBA</t>
+          <t>CKSKA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2904,7 +2932,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2947,12 +2975,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bandung Timur</t>
+          <t>Rancaekek</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BDTMR</t>
+          <t>RCKEK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2961,7 +2989,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3004,17 +3032,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PLTA Parakan</t>
+          <t>Rancaekek Baru</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KIT_PRKAN</t>
+          <t>RCKBA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3022,7 +3050,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -3061,12 +3089,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Parakan</t>
+          <t>Bandung Timur</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PRKAN</t>
+          <t>BDTMR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3079,7 +3107,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -3118,21 +3146,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sumedang</t>
+          <t>PLTA Parakan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SMDNG</t>
+          <t>KIT_PRKAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3154,14 +3182,10 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3179,12 +3203,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kadipaten</t>
+          <t>Parakan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KDPTN</t>
+          <t>PRKAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3193,7 +3217,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3205,11 +3229,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>bus section + kopel</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
@@ -3240,12 +3260,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ujung Berung</t>
+          <t>Sumedang</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UBRNG</t>
+          <t>SMDNG</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3254,11 +3274,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -3266,11 +3286,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>bus section + kopel</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
@@ -3285,7 +3301,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3295,7 +3311,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>BDGSEL;NUBRG</t>
+          <t>NUBRG</t>
         </is>
       </c>
     </row>
@@ -3305,49 +3321,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Ujung Berung</t>
+          <t>Kadipaten</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IBT 1 UBRNG</t>
+          <t>KDPTN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>UBRNG</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>UBRNG4</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>2</v>
-      </c>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV</t>
+          <t>bus section + kopel</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -3370,7 +3372,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>BDGSEL;NUBRG</t>
+          <t>NUBRG</t>
         </is>
       </c>
     </row>
@@ -3380,12 +3382,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ujung Berung (bus 70 kV)</t>
+          <t>Ujung Berung</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UBRNG4</t>
+          <t>UBRNG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3394,11 +3396,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -3406,7 +3408,11 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
@@ -3416,10 +3422,14 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3437,35 +3447,49 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lembur Situ (UP2B Jakban)</t>
+          <t>IBT 150/70 kV Ujung Berung</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LBSTU</t>
+          <t>IBT 1 UBRNG</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>UBRNG</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>UBRNG4</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>2</v>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Pelabuhan Ratu</t>
+          <t>IBT 150/70 kV</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -3474,11 +3498,7 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -3492,7 +3512,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>BDGSEL</t>
+          <t>BDGSEL;NUBRG</t>
         </is>
       </c>
     </row>
@@ -3502,12 +3522,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bogor Baru (UP2B Jakban)</t>
+          <t>Ujung Berung (bus 70 kV)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BGBRU</t>
+          <t>UBRNG4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3516,11 +3536,11 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -3528,22 +3548,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Pelabuhan Ratu</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -3557,7 +3569,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>BDGSEL</t>
+          <t>BDGSEL;NUBRG</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3579,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tajur (UP2B Jakban)</t>
+          <t>Lembur Situ (UP2B Jakban)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TAJUR</t>
+          <t>LBSTU</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3595,7 +3607,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>batas ke UP2B Jakarta &amp; Banten</t>
+          <t>batas ke Subsistem Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
@@ -3632,12 +3644,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lengkong Dar (SS Cirata)</t>
+          <t>Bogor Baru (UP2B Jakban)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LGDAR</t>
+          <t>BGBRU</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3646,7 +3658,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3660,7 +3672,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Cirata 1,2,3</t>
+          <t>batas ke Subsistem Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -3697,12 +3709,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Degung Pakar (SS Cirata)</t>
+          <t>Tajur (UP2B Jakban)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DGPKR</t>
+          <t>TAJUR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3725,7 +3737,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Cirata 1,2,3</t>
+          <t>batas ke UP2B Jakarta &amp; Banten</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -3741,14 +3753,10 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3756,7 +3764,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>BDGSEL;NUBRG</t>
+          <t>BDGSEL</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3774,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Traksi Tagolar</t>
+          <t>Lengkong Dar (SS Cirata)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TRAKSI</t>
+          <t>LGDAR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3780,7 +3788,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3794,7 +3802,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>penyulang traksi</t>
+          <t>batas ke Subsistem Cirata 1,2,3</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -3831,12 +3839,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Garut (SS Tasikmalaya)</t>
+          <t>Degung Pakar (SS Cirata)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GARUT</t>
+          <t>DGPKR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3845,7 +3853,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3859,7 +3867,7 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Tasikmalaya 1,2</t>
+          <t>batas ke Subsistem Cirata 1,2,3</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -3875,10 +3883,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3886,7 +3898,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>NUBRG</t>
+          <t>BDGSEL;NUBRG</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3908,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Seragi (SS Mandirancan)</t>
+          <t>Traksi Tagolar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SRAGI</t>
+          <t>TRAKSI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3910,7 +3922,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3924,7 +3936,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Mandirancan 1,2</t>
+          <t>penyulang traksi</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -3951,7 +3963,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>NUBRG</t>
+          <t>BDGSEL</t>
         </is>
       </c>
     </row>
@@ -3961,12 +3973,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New Kadipaten (SS Mandirancan)</t>
+          <t>Garut (SS Tasikmalaya)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NKDPT</t>
+          <t>GARUT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3989,7 +4001,7 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Mandirancan 1,2</t>
+          <t>batas ke Subsistem Tasikmalaya 1,2</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -4026,12 +4038,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arjawinangun (SS Mandirancan)</t>
+          <t>Seragi (SS Mandirancan)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ARJWN</t>
+          <t>SRAGI</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4040,11 +4052,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -4091,12 +4103,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wayang Windu (SS Bandung Selatan)</t>
+          <t>New Kadipaten (SS Mandirancan)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>WYNDU</t>
+          <t>NKDPT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4119,7 +4131,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>batas ke sisi Bandung Selatan</t>
+          <t>batas ke Subsistem Mandirancan 1,2</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -4156,12 +4168,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gedebage (SS Bandung Selatan)</t>
+          <t>Arjawinangun (SS Mandirancan)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GDBGE</t>
+          <t>ARJWN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4170,11 +4182,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -4184,7 +4196,7 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>batas ke sisi Bandung Selatan</t>
+          <t>batas ke Subsistem Mandirancan 1,2</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -4210,6 +4222,136 @@
         </is>
       </c>
       <c r="S59" t="inlineStr">
+        <is>
+          <t>NUBRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Wayang Windu (SS Bandung Selatan)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>WYNDU</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>batas ke sisi Bandung Selatan</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>NUBRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gedebage (SS Bandung Selatan)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>GDBGE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>batas ke sisi Bandung Selatan</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
         <is>
           <t>NUBRG</t>
         </is>
@@ -7347,12 +7489,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Bandung Selatan- Wayangwindu 1,2 diatas 70% (@77%, kapasitas terpasang 780 A)</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Bandung Selatan- Wayangwindu 1,2 diatas 70% (@77%, kapasitas terpasang 780 A)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7382,12 +7524,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Cianjur - Sukaluyu/ Rajamandala-Cigereleng diatas 50% (@55%, kapasitas terpasang 580 A)</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Cianjur - Sukaluyu/ Rajamandala-Cigereleng diatas 50% (@55%, kapasitas terpasang 580 A)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7417,12 +7559,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[N-1] Hanya ada 1 (Satu) IBT yaitu IBT-1 150/66 kV Wayang Windu, permasalahan kesulitan pemeliharaan IBT jika PLTA PLC tidak beroperasi maksimum maka pembebanan IBT-1,2 Cigereleng mencapai &gt; 50%</t>
+          <t>[BELUM_DITETAPKAN] Hanya ada 1 (Satu) IBT yaitu IBT-1 150/66 kV Wayang Windu, permasalahan kesulitan pemeliharaan IBT jika PLTA PLC tidak beroperasi maksimum maka pembebanan IBT-1,2 Cigereleng mencapai &gt; 50%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7452,12 +7594,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] Kurang andalnya pasokan ke Traksi Tegalluar dikarenakan konfigurasi Traksi Tegalluar tapping di SUTT 150 kV Ujung Berung -Gedebage #1 #2</t>
+          <t>[BELUM_DITETAPKAN] Kurang andalnya pasokan ke Traksi Tegalluar dikarenakan konfigurasi Traksi Tegalluar tapping di SUTT 150 kV Ujung Berung -Gedebage #1 #2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7487,12 +7629,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Ujungberung-Dagopakar diatas 50% (@57%, kapasitas terpasang 580 A) Ketika GI Dagopakar &amp; Bandung Utara dipasok SS Bandung Selatan-New Ujungberung</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Ujungberung-Dagopakar diatas 50% (@57%, kapasitas terpasang 580 A) Ketika GI Dagopakar &amp; Bandung Utara dipasok SS Bandung Selatan-New Ujungberung</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -7522,12 +7664,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] Tegangan terendah di GI 150 kV Cianjur mencapai 137.5 kV dengan kondisi normal kapasitor di GI Cianjur beroperasi, Kapasitor GI Lagadar operasi ke SS Bandung Selatan, dan PLTA Rajamandala sedang kondisi outage)</t>
+          <t>[BELUM_DITETAPKAN] Tegangan terendah di GI 150 kV Cianjur mencapai 137.5 kV dengan kondisi normal kapasitor di GI Cianjur beroperasi, Kapasitor GI Lagadar operasi ke SS Bandung Selatan, dan PLTA Rajamandala sedang kondisi outage)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7627,12 +7769,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Kamojang-Darajat 1,2 diatas 50% (@55%, kapasitas terpasang 580 A). Ketika PLTP DRJAT 1 &amp; 3 atau 2 &amp; 3 memasok ke SS Ujungberung akan meningkatkan pembebanan pada ruas SUTT tersebut</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Kamojang-Darajat 1,2 diatas 50% (@55%, kapasitas terpasang 580 A). Ketika PLTP DRJAT 1 &amp; 3 atau 2 &amp; 3 memasok ke SS Ujungberung akan meningkatkan pembebanan pada ruas SUTT tersebut</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -7662,12 +7804,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[N-1] Bottleneck SUTT 150 kV Jatigede - Rancaekek yang berdampak terhadap jalur evakuasi untuk PLTU CEP dan PLTA Jatigede menjadi terbatas karena kemampuan penghantar di ruas tersebut sebesar 580 A</t>
+          <t>[BELUM_DITETAPKAN] Bottleneck SUTT 150 kV Jatigede - Rancaekek yang berdampak terhadap jalur evakuasi untuk PLTU CEP dan PLTA Jatigede menjadi terbatas karena kemampuan penghantar di ruas tersebut sebesar 580 A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/samples/ss_bdgsel_nubrg_ingest.xlsx
+++ b/samples/ss_bdgsel_nubrg_ingest.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Views" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gardu_Induk_dan_Aset" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jalur_Transmisi" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bay" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7403,6 +7404,600 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kode GI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nama GI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Feeder (GI Induk)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tegangan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Jumlah Sirkit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status Operasi</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>No Kerawanan</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sudut Pandang</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ARJWN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Arjawinangun (SS Mandirancan)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>KDPTN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NUBRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BGBRU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bogor Baru (UP2B Jakban)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CNJUR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BDGSEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DGPKR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Degung Pakar (SS Cirata)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>UBRNG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BDGSEL;NUBRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GARUT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Garut (SS Tasikmalaya)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DRJAT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NUBRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GDBGE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Gedebage (SS Bandung Selatan)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>UBRNG</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BDGSEL;NUBRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LBSTU</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lembur Situ (UP2B Jakban)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CNJUR</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BDGSEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LGDAR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lengkong Dar (SS Cirata)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SKLYU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BDGSEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NKDPT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>New Kadipaten (SS Mandirancan)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JTDGE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NUBRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SRAGI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Seragi (SS Mandirancan)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JTDGE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NUBRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TAJUR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tajur (UP2B Jakban)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CNJUR</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>BDGSEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TRAKSI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Traksi Tagolar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>UBRNG</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>BDGSEL;NUBRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WYNDU</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wayang Windu (SS Bandung Selatan)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KMJNG</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NUBRG</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
